--- a/docs/week9-midterm/journal_paper_candidates_2025_2026.xlsx
+++ b/docs/week9-midterm/journal_paper_candidates_2025_2026.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="12720" activeTab="1"/>
+    <workbookView windowWidth="29320" windowHeight="12880" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Venue Shortlist" sheetId="1" r:id="rId1"/>
     <sheet name="Paper Pool" sheetId="2" r:id="rId2"/>
+    <sheet name="新教学系统对照补充" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="224">
   <si>
     <t>期刊/会议</t>
   </si>
@@ -262,32 +263,14 @@
     <t>Towards accurate and interpretable competency-based assessment: enhancing clinical competency assessment through multimodal AI and anomaly detection.</t>
   </si>
   <si>
-    <r>
-      <t>1. 动机
+    <t>1. 动机
 这篇文章要解决的核心问题是：临床胜任力评估现在太依赖人工专家主观打分，既费人力，也不够稳定，而且很难把“为什么打这个分”解释清楚。传统自动评分研究又大多盯着视频里的技术动作，常把表现粗暴分成高低水平，难以覆盖真实临床里更重要的东西，比如危机识别、沟通协作、持续监测、动态决策。作者因此想做的不是“看几个动作像不像”，而是构建一个更接近真实临床行为的、多模态、可解释的能力评估框架。
 2. 方法
 作者提出的是一个“多模态时间序列 + 异常检测”的框架，而不是直接拿标签做监督回归。具体做法是：从模拟训练中的视频、音频和病人监护仪数据里，提取四类随时间变化的信号——看监护仪的注视行为、空间位置/移动、语音活动、病人生理指标；然后把高水平受训者的表现当成“理想参考轨迹”，训练 MEMTO 这个多变量时间序列异常检测模型去学习“正常/专家式”的行为模式。之后对其他住院医的表现计算偏离专家模式的异常分数，再把异常分数单调映射成 1–5 的胜任力评分。最后再用 SHAP 去解释：模型到底是因为哪些模态、哪些阶段的行为偏离，才给出较差的分数。
 3. 实验设计
 实验对象是 90 名麻醉科住院医，来自 17 家医院。研究场景是高保真模拟考试环境，共设计了 7 个临床模拟场景，每次模拟被切成 4 个固定阶段：初始稳定期、急剧恶化期、ACLS 处理期、复苏后稳定期。每场模拟由有经验的麻醉科认证专家按标准脚本和评分说明打一个 1–5 的总分，这个分数就是“人工真值”。数据采集方面，作者用了双视角视频、每个人佩戴的麦克风，以及病人监护仪读数；再通过现成或改造过的模型把原始多媒体流变成同步时间序列。模型层面，他们主要用 Rank 5 的高分组作为参考标准训练 MEMTO，同时也拿 Rank 1 低分组做对照，检验“用差表现定义正常模式”会不会变差。评估指标用了 Spearman 相关、相对 L2 距离、ICC，还做了 bootstrap 置信区间和 Wilcoxon 检验。
 4. 结果
-结果很明确：这套方法有效，而且多模态明显优于单模态。用 Rank 5 高水平样本做参考训练时，四模态融合（注视+移动+语音+生命体征）和专家评分的一致性最好，Spearman ρ=0.776，Relative L2 distance=0.124，ICC=0.748；如果只用 gaze，效果会明显下降到 ρ=0.286、Relative L2=0.795、ICC=0.157。也就是说，能力评估不是看一个信号就够，沟通、注意力、位置行为和病人生理变化一起看，才更接近专家判断。另一个重要结果是：分数越低的住院医，检测出的异常片段越多、异常分值越高，说明模型确实抓到了“偏离专家行为模式”的程度。SHAP 分析显示，语音/沟通行为和看监护仪的眼神注意是最重要的影响因素；在危机升级阶段，监护仪注视最关键；在复苏阶段，语音和收缩压、SpO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>₂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 的作用变强。作者因此认为，这个系统有潜力成为人工评估的可扩展补充工具，既能给出分数，也能辅助 debriefing，但还不能替代专家，而且目前结论主要限于模拟场景，临床外部泛化仍需进一步验证。</t>
-    </r>
+结果很明确：这套方法有效，而且多模态明显优于单模态。用 Rank 5 高水平样本做参考训练时，四模态融合（注视+移动+语音+生命体征）和专家评分的一致性最好，Spearman ρ=0.776，Relative L2 distance=0.124，ICC=0.748；如果只用 gaze，效果会明显下降到 ρ=0.286、Relative L2=0.795、ICC=0.157。也就是说，能力评估不是看一个信号就够，沟通、注意力、位置行为和病人生理变化一起看，才更接近专家判断。另一个重要结果是：分数越低的住院医，检测出的异常片段越多、异常分值越高，说明模型确实抓到了“偏离专家行为模式”的程度。SHAP 分析显示，语音/沟通行为和看监护仪的眼神注意是最重要的影响因素；在危机升级阶段，监护仪注视最关键；在复苏阶段，语音和收缩压、SpO₂ 的作用变强。作者因此认为，这个系统有潜力成为人工评估的可扩展补充工具，既能给出分数，也能辅助 debriefing，但还不能替代专家，而且目前结论主要限于模拟场景，临床外部泛化仍需进一步验证。</t>
   </si>
   <si>
     <t>可作为我们结构化评分+证据可视化链路的重要方法依据。</t>
@@ -305,48 +288,14 @@
     <t>Can ChatGPT Teach Tendon Repair Suturing? A Comparison With Video Instruction in a Simulation-Based Environment: A Pilot Study.</t>
   </si>
   <si>
-    <r>
-      <t>1. 动机
+    <t>1. 动机
 这篇文章要解决的核心问题，不是“能不能让 AI 给临床学员打分”，而是“能不能把原本主观、费人、难解释的临床能力评估，变成一个更客观、可扩展、可解释的系统”。作者指出，传统临床胜任力评估高度依赖专家现场观察和主观判断；即使在高仿真模拟场景里，评价也仍然很耗费专家资源，而且很难稳定地捕捉到沟通、注意力分配、动态决策这类细粒度能力。现有 AI 评估方法又大多集中在手术视频、动作评分或粗粒度“高/低水平”分类，缺少对真实临床复杂行为的多模态建模，也缺少一个以“专家时序行为模式”为基准的可解释评价框架。作者因此提出：应该把临床表现看成一个多变量时间序列问题，用“偏离专家模式的程度”来衡量能力。
 2. 方法
-作者的方法本质上是一个“多模态时序建模 + 异常检测 + 可解释分析”的框架。输入不是单一视频，而是四类同步时间序列：医生是否注视病人监护仪、医生在模拟空间中的位置/移动、医生的语音活动、病人的生命体征变化。技术上，他们先用视觉和音频管线把原始录音录像转成统一对齐的时间序列：用面部检测和 gaze-target pipeline 提取“是否看监护仪”，用 YOLOv10 + BoT-SORT + TRAM 提取位姿和站位轨迹，用 ESPnet-SE 做语音增强并提取 speech activity，用 DocTR 从监护仪画面中读出心率、血压、SpO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>₂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 等数值。然后用 MEMTO 这个多变量时间序列异常检测模型，只在高水平学员（Rank 5）数据上训练，让模型学到“理想/专家型”的时序模式。之后，把其他人的表现输入进去，若某段行为偏离专家模式，就产生更高 anomaly score。最后再把整体异常程度单调映射到 1–5 的能力评分，并用 SHAP 解释是哪些模态、哪些阶段对异常分数贡献最大。
+作者的方法本质上是一个“多模态时序建模 + 异常检测 + 可解释分析”的框架。输入不是单一视频，而是四类同步时间序列：医生是否注视病人监护仪、医生在模拟空间中的位置/移动、医生的语音活动、病人的生命体征变化。技术上，他们先用视觉和音频管线把原始录音录像转成统一对齐的时间序列：用面部检测和 gaze-target pipeline 提取“是否看监护仪”，用 YOLOv10 + BoT-SORT + TRAM 提取位姿和站位轨迹，用 ESPnet-SE 做语音增强并提取 speech activity，用 DocTR 从监护仪画面中读出心率、血压、SpO₂ 等数值。然后用 MEMTO 这个多变量时间序列异常检测模型，只在高水平学员（Rank 5）数据上训练，让模型学到“理想/专家型”的时序模式。之后，把其他人的表现输入进去，若某段行为偏离专家模式，就产生更高 anomaly score。最后再把整体异常程度单调映射到 1–5 的能力评分，并用 SHAP 解释是哪些模态、哪些阶段对异常分数贡献最大。
 3. 实验设计
 实验对象是 90 名麻醉科住院医师，来自 17 家医院。场景来自以麻醉科国家执照考试为导向的高保真模拟训练。每场模拟按四个阶段展开：初始稳定期、急剧恶化期、ACLS 抢救管理期、复苏后恢复期。每次模拟都由有经验的麻醉科专家按照标准化脚本和评分指导打一个 1–5 的总分，作为“人工真值”。作者采集了双视角视频、监护仪画面和多通道音频，并把所有流同步到统一时间轴。评估上，作者做了几层设计：一是用 Rank 5 作为“专家参考集”训练 MEMTO；二是专门拿 Rank 1 训练做对照，看“用差的表现当正常模板”会不会让模型变差；三是做模态消融，依次比较 gaze、gaze+movement、再加 speech、再加 vitals 的效果；四是用 LOOCV 验证稳定性。评价指标包括 Spearman 相关、相对 L2 距离、ICC(1,k)，并用 bootstrap 置信区间和 Wilcoxon 检验验证统计显著性。
 4. 结果
-多模态、专家锚定的方案有效，而且明显优于单模态。总体上，模型给出的能力分数与专家评分有较强一致性，文中摘要给出的主要结果是 Spearman ρ = 0.75、ICC = 0.75、Relative L2-distance = 0.124；详细表格里，四模态联合时达到 ρ = 0.776、ICC = 0.748、R-L2 = 0.124。随着人工评分从 Rank 1 提高到 Rank 5，异常分数整体明显下降，说明模型确实在捕捉“越像专家，越少异常”这个趋势。消融实验也表明，单独用 gaze 效果很弱，但逐步加入 movement、speech 和 vitals 后性能持续提升；相反，如果用 Rank 1 的差表现去训练“正常模式”，模型与专家评分的一致性会显著变差，说明“基准是谁”非常关键。解释性分析方面，SHAP 显示：语言活动在初始阶段、ACLS 阶段和恢复阶段都很重要；在病情急剧恶化阶段，盯监护仪的视觉注意最关键；在抢救和恢复阶段，血压和 SpO</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Times New Roman"/>
-        <charset val="134"/>
-      </rPr>
-      <t>₂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t xml:space="preserve"> 等生命体征也会成为重要辅助特征。作者据此认为，这个系统不只是能“打一个分”，还能够告诉教师“这个分主要是因为什么行为偏离专家模式而来的”，更适合用于教学反馈和复盘。</t>
-    </r>
+多模态、专家锚定的方案有效，而且明显优于单模态。总体上，模型给出的能力分数与专家评分有较强一致性，文中摘要给出的主要结果是 Spearman ρ = 0.75、ICC = 0.75、Relative L2-distance = 0.124；详细表格里，四模态联合时达到 ρ = 0.776、ICC = 0.748、R-L2 = 0.124。随着人工评分从 Rank 1 提高到 Rank 5，异常分数整体明显下降，说明模型确实在捕捉“越像专家，越少异常”这个趋势。消融实验也表明，单独用 gaze 效果很弱，但逐步加入 movement、speech 和 vitals 后性能持续提升；相反，如果用 Rank 1 的差表现去训练“正常模式”，模型与专家评分的一致性会显著变差，说明“基准是谁”非常关键。解释性分析方面，SHAP 显示：语言活动在初始阶段、ACLS 阶段和恢复阶段都很重要；在病情急剧恶化阶段，盯监护仪的视觉注意最关键；在抢救和恢复阶段，血压和 SpO₂ 等生命体征也会成为重要辅助特征。作者据此认为，这个系统不只是能“打一个分”，还能够告诉教师“这个分主要是因为什么行为偏离专家模式而来的”，更适合用于教学反馈和复盘。</t>
   </si>
   <si>
     <t>可支持我们“AI反馈相对传统材料的增益”论证。</t>
@@ -381,6 +330,438 @@
   </si>
   <si>
     <t>教育数据挖掘领域公认顶会（EDM）</t>
+  </si>
+  <si>
+    <t>教学系统类型</t>
+  </si>
+  <si>
+    <t>对照方式</t>
+  </si>
+  <si>
+    <t>A Randomized Controlled Trial of a Deep Language Learning Model-Based Simulation Tool for Undergraduate Medical Students in Surgery.</t>
+  </si>
+  <si>
+    <t>大语言模型虚拟病人/软件模拟问诊系统</t>
+  </si>
+  <si>
+    <t>DLM虚拟病人训练 + 常规临床学习 vs 仅常规临床学习</t>
+  </si>
+  <si>
+    <t>动机：外科病史采集是临床训练核心能力，但真实病人和标准化病人资源有限，学生很难反复练习并获得稳定反馈。方法：研究开展随机对照试验，90名外科轮转本科医学生分为两组；干预组在常规临床学习之外，增加3次基于深度语言模型的虚拟病人问诊训练，控制组只接受标准临床学习；结局用真人标准化病人的OSCE病史采集考试和盲法评分评估。结果：两组基线相近，但干预组OSCE分数显著提升，学生普遍认为虚拟病人病史细节丰富、能提升沟通信心并愿意继续使用。</t>
+  </si>
+  <si>
+    <t>非常贴近你们“线上问诊+病例生成+训练反馈”模块，可直接参考其实验设计：AI虚拟病人作为补充训练系统，与传统临床学习对照。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103629</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40729832/</t>
+  </si>
+  <si>
+    <t>补充候选</t>
+  </si>
+  <si>
+    <t>AI Teaches Surgical Diagnostic Reasoning to Medical Students: Evidence from an Experiment Using a Fully Automated, Low-Cost Feedback System.</t>
+  </si>
+  <si>
+    <t>全自动AI题目生成与个性化反馈平台</t>
+  </si>
+  <si>
+    <t>AI生成MCQ+个性化反馈+间隔重复 vs 非干预对照</t>
+  </si>
+  <si>
+    <t>动机：诊断推理教学通常依赖教师设计题目和人工反馈，成本高且难以规模化。方法：研究构建一个低成本Web平台，由AI自动生成腹痛相关外科诊断MCQ和个性化反馈，并让一年级医学生连续5天练习；对照组为二年级医学生，只完成同样的OSVE诊断推理评估。结果：干预组在即时测试和2周后测试中均显著优于对照组；专家事后审核确认AI题目准确，反馈问题极少，总成本仅0.51美元。</t>
+  </si>
+  <si>
+    <t>非常贴近你们“关卡生成+即时反馈+低成本规模化训练”的论文叙事，可用来论证AI能生成训练题和反馈闭环。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103639</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40768987/</t>
+  </si>
+  <si>
+    <t>Effect of Artificial Intelligence-Augmented Human Instruction on Feedback Frequency and Surgical Performance During Simulation Training.</t>
+  </si>
+  <si>
+    <t>AI增强人工带教的VR神经外科仿真训练</t>
+  </si>
+  <si>
+    <t>AI增强人工反馈 vs AI导师反馈 vs 脚本化人工反馈</t>
+  </si>
+  <si>
+    <t>动机：纯AI反馈可扩展，但可能缺少教师判断；纯人工反馈又成本高且不稳定。方法：研究基于NeuroVR沉浸式神经外科模拟器，把医学生随机分到AI导师、脚本化人工指导、AI错误数据增强的人类个性化指导三组，并比较训练中反馈频率与技术表现。结果：AI增强人工指导组在重复训练后反馈需求下降，说明错误减少，同时技能表现改善；研究支持“AI检测错误+人类教师解释反馈”的混合教学系统。</t>
+  </si>
+  <si>
+    <t>这和你们“结构化评分先算证据，再由LLM/教师化语言输出反馈”非常像，可作为混合反馈系统的强参考。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103743</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41066879/</t>
+  </si>
+  <si>
+    <t>Augmented reality enhances competency-based training in simulated vaginal birth: A multicenter randomized controlled trial.</t>
+  </si>
+  <si>
+    <t>增强现实AR程序性技能预训练系统</t>
+  </si>
+  <si>
+    <t>AR训练 vs 传统文本/视频准备</t>
+  </si>
+  <si>
+    <t>动机：高保真模拟器稀缺，程序性技能训练需要更可扩展的预训练方式。方法：研究在智利和哥伦比亚两所大学开展多中心随机对照试验，401名医学和助产学生分为AR训练组和传统文本/视频准备组，随后都进入高保真分娩模拟，并用DOPS清单盲法评分。结果：AR组DOPS总分、关键任务完成度和达到最低胜任阈值比例均显著高于传统组，说明AR能提升进入高保真模拟前的技能准备质量。</t>
+  </si>
+  <si>
+    <t>可借鉴到你们的光凝训练：先用交互式系统学习参数、危险区、操作流程，再进入完整手术仿真。</t>
+  </si>
+  <si>
+    <t>10.1080/0142159X.2026.2630982</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41749486/</t>
+  </si>
+  <si>
+    <t>The Application Value of Three-Dimensional Reconstruction Technology in Liver Surgery Teaching.</t>
+  </si>
+  <si>
+    <t>三维重建+虚拟手术规划教学系统</t>
+  </si>
+  <si>
+    <t>3D重建动态模型+虚拟手术规划 vs 传统图谱/实体模型/视频教学</t>
+  </si>
+  <si>
+    <t>动机：肝脏解剖复杂，传统图谱、实体模型和视频难以帮助学员形成空间结构与手术路径理解。方法：研究随机分配50名肝胆外科轮转医师到传统教学组或3D教学组；3D组使用三维重建动态肝脏模型、虚拟手术规划和手术视频，传统组使用解剖图谱、实体模型和视频；两组师资、病例、学时一致。结果：3D组理论、实践和总分均显著更高，并在满意度、学习兴趣、知识获得效率和内容掌握方面明显优于传统组。</t>
+  </si>
+  <si>
+    <t>和你们眼底图像/危险区/光斑路径可视化很近：说明三维/可交互医学图像能把被动学习转成主动探索。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103847</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41456545/</t>
+  </si>
+  <si>
+    <t>Evaluating a digital serious game for learning medical terminology in a randomized controlled trial.</t>
+  </si>
+  <si>
+    <t>数字严肃游戏教学系统</t>
+  </si>
+  <si>
+    <t>严肃游戏+讲授 vs 传统讲授</t>
+  </si>
+  <si>
+    <t>动机：医学术语抽象且记忆负担高，传统讲授容易让学生被动记忆。方法：研究开展随机对照试验，60名健康相关专业本科生分为传统教学组和MedQuiz严肃游戏辅助教学组，比较术语学习即时成绩、用户体验、可用性和游戏化学习感受。结果：干预组后测成绩显著高于传统组，系统可用性评分高，学生参与感强；研究支持严肃游戏作为可规模化、提高短期学习效果的教学工具。</t>
+  </si>
+  <si>
+    <t>可为你们“教育游戏不是娱乐外壳，而是提高参与和学习效果的教学系统”提供顶刊证据。</t>
+  </si>
+  <si>
+    <t>10.1038/s41746-026-02525-5</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41942718/</t>
+  </si>
+  <si>
+    <t>ChatGPT实时步骤指导系统</t>
+  </si>
+  <si>
+    <t>ChatGPT对话式指导 vs 结构化视频教学</t>
+  </si>
+  <si>
+    <t>动机：大模型能否独立承担程序性技能教学仍缺少证据，尤其是复杂缝合这类需要示范和空间理解的技能。方法：研究将具备基础缝合能力的医学生分为ChatGPT指导组和视频教学组，两组都在肌腱模拟器上练习5小时，用肌腱特异OSATS、满意度和自信心评价。结果：视频组技术得分、达标率、满意度和自信心均显著优于ChatGPT组；结论是大模型目前不适合单独替代技能示范，但可作为混合教学中的辅助答疑。</t>
+  </si>
+  <si>
+    <t>对你们很有价值，因为它提醒论文不能盲目宣称LLM万能；LLM应服务于结构化评分后的反馈表达，而不是替代仿真训练本身。</t>
+  </si>
+  <si>
+    <t>实时语音AI虚拟病人系统</t>
+  </si>
+  <si>
+    <t>AI虚拟病人 vs 标准化病人 vs 同伴角色扮演</t>
+  </si>
+  <si>
+    <t>动机：沟通训练需要真实病人互动，但标准化病人成本高、同伴角色扮演真实感低。方法：研究基于实时语音生成AI构建虚拟病人，134名住院医随机分到AI虚拟病人、标准化病人或同伴角色扮演组，在相同SPIKES框架下训练并比较沟通表现、自我效能和真实感。结果：AI虚拟病人组显著优于同伴角色扮演，表现接近标准化病人；语言真实度较好，但情绪与情境真实感仍弱于标准化病人。</t>
+  </si>
+  <si>
+    <t>直接对应你们“游戏内手机问诊”的目标：用AI虚拟病人扩展真实问诊训练，同时保留专家审核和情绪真实度改进空间。</t>
+  </si>
+  <si>
+    <t>The Application of Virtual Simulation Teaching in the Education of Pediatric Acute Intussusception.</t>
+  </si>
+  <si>
+    <t>虚拟仿真儿科急症教学系统</t>
+  </si>
+  <si>
+    <t>虚拟仿真教学 vs 传统课堂教学</t>
+  </si>
+  <si>
+    <t>动机：儿科急性肠套叠这类外科急症依赖情境判断和操作决策，传统课堂讲授与有限观摩很难提供足够实践。方法：研究设计随机对照试验，比较传统教学与基于计算机3D模型、交互仿真和可重复操作环境的虚拟仿真教学，评价理论成绩、模拟操作完成时间、操作完成度、学习动机与教学反馈质量。结果：公开摘要和文章片段显示，虚拟仿真组在理论与实践应用能力、学习积极性和反馈质量上优于传统课堂教学。</t>
+  </si>
+  <si>
+    <t>与光凝项目非常接近：都是小众高风险手术/急症场景，用虚拟仿真替代难以反复获得的真实病例训练。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103536</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40449374/</t>
+  </si>
+  <si>
+    <t>Eye Movement Modeling Examples in Robotic Surgery Training-A Randomized Controlled Study.</t>
+  </si>
+  <si>
+    <t>专家眼动建模视频教学系统</t>
+  </si>
+  <si>
+    <t>带专家眼动叠加的视频 vs 普通手术视频</t>
+  </si>
+  <si>
+    <t>动机：机器人手术学习中，学生不仅要看见画面，还要知道专家把注意力放在哪里。方法：研究随机分配137名四年级医学生观看同一机器人前列腺切除视频；实验组视频叠加专家眼动轨迹，控制组观看无眼动叠加视频；随后用解剖标志识别任务和学习材料停留时间评价。结果：眼动组学习时间更长，并在部分视觉识别学习指标上表现更好，说明专家注意路径可作为多媒体教学提示。</t>
+  </si>
+  <si>
+    <t>可迁移到你们：在术后复盘里不仅展示玩家与标准答案差异，还可以展示专家视线/关注区域/推荐打点路径。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103539</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40381515/</t>
+  </si>
+  <si>
+    <t>Effects of Real Time Biofeedback on Open Surgery Suturing Skills Acquisition.</t>
+  </si>
+  <si>
+    <t>实时视觉/触觉生物反馈训练系统</t>
+  </si>
+  <si>
+    <t>实时视觉/触觉反馈 vs 无实时反馈控制</t>
+  </si>
+  <si>
+    <t>动机：初学者练习缝合时常不知道自己对组织施加了多大力，也就难以及时纠正危险动作。方法：研究开展随机对照试验，27名无经验医学生在模拟组织垫上练习打结，分为控制组、视觉反馈组和触觉反馈组；系统通过力测量设备提取10个力相关指标，并追踪学习曲线。结果：三组均进步，但视觉和触觉反馈组最终组织处理能力更好，学习曲线显示干预组达到更高熟练水平。</t>
+  </si>
+  <si>
+    <t>与你们光凝能量/重叠/危险区反馈很像：实时反馈可以把不可见风险转成学习者可理解的纠错信号。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103738</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41072244/</t>
+  </si>
+  <si>
+    <t>Improving Medical Student Performance With Unsupervised Simulation and Remote Asynchronous Feedback.</t>
+  </si>
+  <si>
+    <t>无监督仿真+远程异步反馈系统</t>
+  </si>
+  <si>
+    <t>自练+远程异步反馈 vs 现场集中工作坊+当面反馈</t>
+  </si>
+  <si>
+    <t>动机：临床操作技能训练受教师时间和场地限制，学生难以反复练习并获得及时指导。方法：研究将三年级医学生随机到胸腔穿刺或腹腔穿刺任务，并进一步分配到无监督仿真+远程异步反馈组或2小时现场工作坊组；训练后用OSATS评价技能。结果：异步反馈组在两项操作中的通过率均显著高于现场工作坊组，说明非同步数字化反馈可以提高训练效率并降低师资同步负担。</t>
+  </si>
+  <si>
+    <t>这与项目的“玩家提交日志/图像后系统自动复盘”非常接近，可支持异步反馈比传统一次性课堂更适合反复技能训练。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2024.103302</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39442366/</t>
+  </si>
+  <si>
+    <t>Assessing the Efficacy of Enhanced Versus Standard Three-Dimensional Training Models in Laparoscopic Skills Acquisition: A Randomized Controlled Trial of Novice Medical Students.</t>
+  </si>
+  <si>
+    <t>增强型三维低保真训练模型</t>
+  </si>
+  <si>
+    <t>增强3D模型 vs 标准3D训练模型</t>
+  </si>
+  <si>
+    <t>动机：腹腔镜训练受二维视觉和深度知觉限制，新手需要更好的空间线索来适应操作。方法：研究将65名新手医学生随机分到增强3D模型组或标准LapPass 3D模型组，完成抓取操作和腔内缝合任务，并在基线、中期、训练后用GOALS、完成时间和错误数评价。结果：两组均进步，但增强3D组在GOALS总分和深度知觉维度提升更大，部分时间和错误指标也更优。</t>
+  </si>
+  <si>
+    <t>可类比你们眼底球面结构、光斑深度/焦距模拟：训练模型的空间真实性会影响技能获得。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2024.08.028</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/39393177/</t>
+  </si>
+  <si>
+    <t>Rapid Cycle Deliberate Practice With Spaced Training Achieves Comparable Results in Achieving Simple Laparoscopic Skills to Traditional Weekly Training and Saves Time.</t>
+  </si>
+  <si>
+    <t>快速循环刻意练习+间隔训练方案</t>
+  </si>
+  <si>
+    <t>RCDP+间隔训练 vs 传统每周仿真训练</t>
+  </si>
+  <si>
+    <t>动机：传统每周仿真训练耗时长，医学课程中很难安排足够练习；如果更高频、更短周期的反馈循环能达到同等效果，就更适合课程嵌入。方法：研究采用准实验试点，38名学生随机接受RCDP+间隔训练或传统每周训练，均完成4次腹腔镜缝合仿真训练，并由盲法视频评分比较OSATS和GRC。结果：两组技能评分无显著差异，但RCDP+间隔训练节省时间，说明短周期反馈循环可在更少时间内达到传统训练效果。</t>
+  </si>
+  <si>
+    <t>可启发你们关卡设计：小步练习、快速反馈、多轮修正，比一次长时间训练更适合游戏化系统。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103686</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40987232/</t>
+  </si>
+  <si>
+    <t>A Pilot Randomized Cross-Over Trial Focused on Colonoscopy Skill Acquisition Using High Fidelity Versus Low Fidelity Simulators in Nigeria.</t>
+  </si>
+  <si>
+    <t>高/低保真结肠镜模拟器训练系统</t>
+  </si>
+  <si>
+    <t>低保真模拟器 vs 高保真模拟器</t>
+  </si>
+  <si>
+    <t>动机：低中收入地区需要扩大内镜训练，但高保真模拟器价格高、可及性差。方法：研究在尼日利亚结肠镜培训项目中开展随机交叉试验，参与者完成在线课程和4天线下训练，分别接触高保真和本地开发低保真模拟器，并用MCSAT和GAGES评分评价技能。结果：两类模拟器训练后技能均提高，最终考试未显示显著差异；低保真模型在资源受限场景中可能提供可行替代。</t>
+  </si>
+  <si>
+    <t>对你们有现实意义：不一定追求最昂贵真实设备，关键是教学目标、反馈指标和可重复练习。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2026.103932</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41990515/</t>
+  </si>
+  <si>
+    <t>AI at the bedside: Randomised controlled trial of ChatGPT's impact on student performance in real-patient clinical exams.</t>
+  </si>
+  <si>
+    <t>床旁ChatGPT辅助临床考试系统</t>
+  </si>
+  <si>
+    <t>允许ChatGPT辅助 vs 不允许数字工具</t>
+  </si>
+  <si>
+    <t>动机：生成式AI进入临床学习很快，但它在真实病人床旁考试中是否提升学生表现仍不清楚。方法：研究在四家教学医院开展平行随机对照试验，73名终年级医学生在真实病人临床考试中被分到允许使用GPT-4o或不允许数字工具组，评分覆盖病史、查体、鉴别诊断、检查、处理和沟通。结果：ChatGPT组整体表现与对照组无显著差异，学生使用频率和感知帮助也不预测成绩；说明“允许使用AI”本身不足以提升表现，需要明确教学设计和训练方式。</t>
+  </si>
+  <si>
+    <t>对你们很重要：论文叙事不能写成“接入LLM就有效”，必须强调结构化场景、评分证据和反馈闭环。</t>
+  </si>
+  <si>
+    <t>10.1080/0142159X.2026.2652061</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/42010936/</t>
+  </si>
+  <si>
+    <t>Artificial Intelligence-based online platform assists blood cell morphology learning: A mixed-methods sequential explanatory designed research.</t>
+  </si>
+  <si>
+    <t>AI在线形态学学习平台</t>
+  </si>
+  <si>
+    <t>AI在线平台学习 vs 显微镜学习顺序交叉对照</t>
+  </si>
+  <si>
+    <t>动机：血细胞形态学习依赖大量图像比较和教师经验，传统显微镜学习可及性和反馈效率有限。方法：研究采用混合方法和交叉设计，31名三年级医学生随机进入两种学习顺序，分别体验AI在线平台学习和显微镜学习，并进行前后测和访谈。结果：两组在AI平台学习后成绩均显著提升，学生认为平台可用性高，AI能引导他们比较细胞异同并加深理解。</t>
+  </si>
+  <si>
+    <t>虽然不是手术，但和你们“眼底图像+AI辅助训练”很近，可作为医学图像识别教育系统对比传统显微镜教学的参考。</t>
+  </si>
+  <si>
+    <t>10.1080/0142159X.2023.2190483</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/36971649/</t>
+  </si>
+  <si>
+    <t>Evaluation of a Cost-Effective Virtual Reality Training System in Oral Maxillofacial Surgery: A Pilot Study.</t>
+  </si>
+  <si>
+    <t>低成本360° VR手术视频训练系统</t>
+  </si>
+  <si>
+    <t>360° VR视频 vs 普通2D手术视频</t>
+  </si>
+  <si>
+    <t>动机：复杂口腔颌面外科手术实践机会有限，昂贵VR系统又限制普及。方法：研究制作复杂手术的360° VR和2D视频并发布到YouTube，让参加尸体课程的15名学员观看两种格式后比较理解、空间感、易用性和偏好。结果：VR在空间感、直观性和用户偏好上更好，但部分学员出现眩晕，且样本小导致理解提升未达统计显著。</t>
+  </si>
+  <si>
+    <t>可参考你们如何在低成本条件下增强手术空间理解，同时注意VR/沉浸式体验的副作用和评价设计。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103505</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40239444/</t>
+  </si>
+  <si>
+    <t>Concurrent versus terminal feedback: The effect of feedback delivery on lumbar puncture skills in simulation training.</t>
+  </si>
+  <si>
+    <t>模拟操作中的实时反馈教学方式</t>
+  </si>
+  <si>
+    <t>操作中即时反馈 vs 操作后终末反馈</t>
+  </si>
+  <si>
+    <t>动机：仿真教学中反馈很重要，但到底应在操作过程中即时给，还是结束后统一给，过去证据不一致。方法：研究将32名新手医学生随机分为即时反馈组和终末反馈组，训练腰椎穿刺，并在习得后测、保持测试和迁移测试中由盲法专家用清单评分，同时测量认知负荷和焦虑。结果：即时反馈组在腰穿技能清单得分上显著高于终末反馈组，认知负荷和焦虑无显著差异，学生也更满意学习体验。</t>
+  </si>
+  <si>
+    <t>可直接指导你们光凝系统反馈时机设计：哪些风险必须实时提示，哪些内容适合术后复盘。</t>
+  </si>
+  <si>
+    <t>10.1080/0142159X.2023.2189540</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/36931315/</t>
+  </si>
+  <si>
+    <t>Impact of Preoperative Warm-Up on Surgical Performance of Resident Physicians: A Randomized Controlled Trial.</t>
+  </si>
+  <si>
+    <t>术前训练箱热身模拟系统</t>
+  </si>
+  <si>
+    <t>术前10分钟模拟器热身 vs 无热身</t>
+  </si>
+  <si>
+    <t>动机：住院医进入真实手术前，短时间模拟器热身是否能改善即时手术表现仍需验证。方法：研究将105名无腹腔镜经验的一年级普外科住院医分为热身组和对照组；热身组术前用低成本训练箱练习10分钟，对照组直接操作，并在猪模型手术中比较表现。结果：热身组胆囊切除效率、胆囊切除解剖时间和左肾切除解剖时间等指标显著改善。</t>
+  </si>
+  <si>
+    <t>可支持你们设计“正式关卡前的试打/热身/调参”机制，把练习与真实任务表现连接起来。</t>
+  </si>
+  <si>
+    <t>10.1016/j.jsurg.2025.103501</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/40184830/</t>
+  </si>
+  <si>
+    <t>Comparing different retrieval practice strategies using virtual patients: A stratified randomized trial.</t>
+  </si>
+  <si>
+    <t>虚拟病人平台复习训练系统</t>
+  </si>
+  <si>
+    <t>重做虚拟病例 vs 选择题复习 vs 简答题复习</t>
+  </si>
+  <si>
+    <t>动机：虚拟病人系统常用于初次学习，但学习后怎样复习最能促进长期保持和迁移并不清楚。方法：80名五年级医学生先在Paciente 360虚拟病人平台完成两个病例，一周后随机进入重做病例、选择题或简答题三种提取练习条件，六周后完成包含旧题和新题的保持/迁移测试。结果：简答题组从基线到延迟测试提升最明显，虚拟病例重做和选择题组更多是保持水平；新题和旧题表现相近，提示虚拟病人可支持迁移学习。</t>
+  </si>
+  <si>
+    <t>可用于你们设计复盘后的二次训练：不一定只让玩家重打一遍，也可以加入诊断推理和参数解释题。</t>
+  </si>
+  <si>
+    <t>10.1080/0142159X.2025.2607517</t>
+  </si>
+  <si>
+    <t>https://pubmed.ncbi.nlm.nih.gov/41503782/</t>
   </si>
 </sst>
 </file>
@@ -393,7 +774,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -562,18 +943,25 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -913,7 +1301,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
@@ -937,16 +1325,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
@@ -955,94 +1343,106 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1404,138 +1804,138 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" ht="50" customHeight="1" spans="1:5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="50" customHeight="1" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" ht="50" customHeight="1" spans="1:5">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" ht="50" customHeight="1" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="6" ht="50" customHeight="1" spans="1:5">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1" spans="1:5">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="B7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" ht="50" customHeight="1" spans="1:5">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="6" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1564,345 +1964,1340 @@
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1" spans="1:12">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="2" ht="170" customHeight="1" spans="1:12">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="6">
         <v>2026</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="6">
         <v>4.94</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="6">
         <v>4.8</v>
       </c>
     </row>
     <row r="3" ht="170" customHeight="1" spans="1:12">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="6">
         <v>2026</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="6">
         <v>4.94</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L3" s="2">
+      <c r="L3" s="6">
         <v>4.8</v>
       </c>
     </row>
     <row r="4" ht="170" customHeight="1" spans="1:12">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="6">
         <v>2026</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="6">
         <v>4.94</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="2">
+      <c r="L4" s="6">
         <v>4.8</v>
       </c>
     </row>
     <row r="5" ht="170" customHeight="1" spans="1:12">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="6">
         <v>2026</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="6">
         <v>4.88</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="2">
+      <c r="L5" s="6">
         <v>4.9</v>
       </c>
     </row>
     <row r="6" ht="170" customHeight="1" spans="1:12">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="6">
         <v>2026</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="F6" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="6">
         <v>4.88</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="L6" s="2">
+      <c r="L6" s="6">
         <v>4.9</v>
       </c>
     </row>
     <row r="7" ht="170" customHeight="1" spans="1:12">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="6">
         <v>2026</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="F7" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="6">
         <v>4.88</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="2">
+      <c r="L7" s="6">
         <v>4.9</v>
       </c>
     </row>
     <row r="8" ht="170" customHeight="1" spans="1:12">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="6">
         <v>2026</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="6">
         <v>4.85</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="L8" s="2">
+      <c r="L8" s="6">
         <v>4.8</v>
       </c>
     </row>
     <row r="9" ht="170" customHeight="1" spans="1:12">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="6">
         <v>2025</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="H9" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="6">
         <v>4.82</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="L9" s="2">
+      <c r="L9" s="6">
         <v>4.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="72" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="105" customWidth="1"/>
+    <col min="6" max="6" width="64" customWidth="1"/>
+    <col min="7" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="28" customWidth="1"/>
+    <col min="10" max="10" width="56" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="13" max="13" width="38" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" spans="1:14">
+      <c r="A1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="135" customHeight="1" spans="1:14">
+      <c r="A2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="K2" s="5">
+        <v>5</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N2" s="5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="3" ht="135" customHeight="1" spans="1:14">
+      <c r="A3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="6">
+        <v>4.98</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="4" ht="135" customHeight="1" spans="1:14">
+      <c r="A4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G4" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="K4" s="6">
+        <v>4.96</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N4" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" ht="135" customHeight="1" spans="1:14">
+      <c r="A5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2026</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="K5" s="7">
+        <v>4.94</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="7">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" ht="135" customHeight="1" spans="1:14">
+      <c r="A6" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="8">
+        <v>2026</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="K6" s="8">
+        <v>4.93</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N6" s="8">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" ht="135" customHeight="1" spans="1:14">
+      <c r="A7" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G7" s="8">
+        <v>2026</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="K7" s="8">
+        <v>4.92</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="N7" s="8">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1" spans="1:14">
+      <c r="A8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="G8" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="K8" s="6">
+        <v>4.9</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="9" ht="135" customHeight="1" spans="1:14">
+      <c r="A9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="K9" s="6">
+        <v>4.9</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="6">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="135" customHeight="1" spans="1:14">
+      <c r="A10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G10" s="5">
+        <v>2025</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="J10" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="K10" s="5">
+        <v>4.88</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="N10" s="5">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="11" ht="135" customHeight="1" spans="1:14">
+      <c r="A11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G11" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="6">
+        <v>4.86</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="12" ht="135" customHeight="1" spans="1:14">
+      <c r="A12" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G12" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="6">
+        <v>4.86</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="13" ht="135" customHeight="1" spans="1:14">
+      <c r="A13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2024</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K13" s="6">
+        <v>4.85</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N13" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="14" ht="135" customHeight="1" spans="1:14">
+      <c r="A14" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G14" s="6">
+        <v>2024</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K14" s="6">
+        <v>4.84</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N14" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="15" ht="135" customHeight="1" spans="1:14">
+      <c r="A15" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="K15" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N15" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="16" ht="135" customHeight="1" spans="1:14">
+      <c r="A16" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G16" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K16" s="6">
+        <v>4.78</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N16" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="17" ht="135" customHeight="1" spans="1:14">
+      <c r="A17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G17" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="K17" s="6">
+        <v>4.76</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="6">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="18" ht="135" customHeight="1" spans="1:14">
+      <c r="A18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="6">
+        <v>2023</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="K18" s="6">
+        <v>4.74</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M18" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="6">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="19" ht="135" customHeight="1" spans="1:14">
+      <c r="A19" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="G19" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="K19" s="6">
+        <v>4.7</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N19" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="20" ht="135" customHeight="1" spans="1:14">
+      <c r="A20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G20" s="6">
+        <v>2023</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="K20" s="6">
+        <v>4.68</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M20" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" s="6">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="21" ht="135" customHeight="1" spans="1:14">
+      <c r="A21" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" s="6">
+        <v>2025</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K21" s="6">
+        <v>4.66</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N21" s="6">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="22" ht="135" customHeight="1" spans="1:14">
+      <c r="A22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G22" s="6">
+        <v>2026</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="K22" s="6">
+        <v>4.64</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="M22" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" s="6">
+        <v>4.9</v>
       </c>
     </row>
   </sheetData>
